--- a/data/ter_annualCAPAD.xlsx
+++ b/data/ter_annualCAPAD.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_MONASH_UNI\_Y3S1\FIT3179\DV2_repo\FIT3179_DV2\data\CAPAD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_MONASH_UNI\_Y3S1\FIT3179\DV2_repo\FIT3179_DV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63C11A5-CA62-4CD5-8A14-7FDAF099C7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E6325C-0D06-42A1-BD80-1969D254483E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11448" yWindow="0" windowWidth="11664" windowHeight="12336" xr2:uid="{6FE64F88-4AA4-4595-983D-FC8D322E0C66}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6FE64F88-4AA4-4595-983D-FC8D322E0C66}"/>
   </bookViews>
   <sheets>
     <sheet name="Terrestrial" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="22">
   <si>
     <t>Year</t>
   </si>
@@ -82,6 +82,30 @@
   <si>
     <t>Not Reported</t>
   </si>
+  <si>
+    <t>IUCN FULL</t>
+  </si>
+  <si>
+    <t>Ia Strict Nature Reserve</t>
+  </si>
+  <si>
+    <t>Ib Wilderness Area</t>
+  </si>
+  <si>
+    <t>II National Park</t>
+  </si>
+  <si>
+    <t>III Natural Monument</t>
+  </si>
+  <si>
+    <t>IV Habitat/ Species Management Area</t>
+  </si>
+  <si>
+    <t>V Protected Landscape/ Seascape</t>
+  </si>
+  <si>
+    <t>VI Managed Resource Protected Area</t>
+  </si>
 </sst>
 </file>
 
@@ -91,8 +115,8 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0000"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -2915,19 +2939,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2347">
@@ -5609,16 +5627,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD5E0B53-5E04-4DB6-B23F-25EFF5247822}">
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="2" width="18.21875" customWidth="1"/>
-    <col min="3" max="3" width="14.21875" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" customWidth="1"/>
+    <col min="2" max="3" width="18.21875" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
+    <col min="5" max="5" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5626,787 +5644,949 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="10">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>2014</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="3">
         <v>16137986.912715601</v>
       </c>
-      <c r="D2" s="5">
+      <c r="E2" s="1">
         <v>2.0990402049216912</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2014</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3">
         <v>5173202.7828957904</v>
       </c>
-      <c r="D3" s="5">
+      <c r="E3" s="1">
         <v>0.67286958951212816</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>2014</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3">
         <v>38053577.770896003</v>
       </c>
-      <c r="D4" s="5">
+      <c r="E4" s="1">
         <v>4.9495634191702305</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>2014</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3">
         <v>8060171.8255562503</v>
       </c>
-      <c r="D5" s="5">
+      <c r="E5" s="1">
         <v>1.0483726881132209</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>2014</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="3">
         <v>3107345.996673</v>
       </c>
-      <c r="D6" s="5">
+      <c r="E6" s="1">
         <v>0.40416715002289799</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>2014</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3">
         <v>7921640.8123816503</v>
       </c>
-      <c r="D7" s="5">
+      <c r="E7" s="1">
         <v>1.0303541974641235</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="10">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>2014</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="3">
         <v>59047220.9767894</v>
       </c>
-      <c r="D8" s="5">
+      <c r="E8" s="1">
         <v>7.6801704877774091</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>2014</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="3">
         <v>404</v>
       </c>
-      <c r="D9" s="5">
+      <c r="E9" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>2016</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="3">
         <v>16013251.879867001</v>
       </c>
-      <c r="D10" s="5">
+      <c r="E10" s="1">
         <v>2.0828109792686607</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="10">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>2016</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="3">
         <v>3841430.0082359998</v>
       </c>
-      <c r="D11" s="5">
+      <c r="E11" s="1">
         <v>0.49964695848601715</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>2016</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="3">
         <v>41575719.629199997</v>
       </c>
-      <c r="D12" s="5">
+      <c r="E12" s="1">
         <v>5.4076689709456165</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="10">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>2016</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="3">
         <v>8484566.3001099993</v>
       </c>
-      <c r="D13" s="5">
+      <c r="E13" s="1">
         <v>1.1035702165167443</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>2016</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="3">
         <v>2090374.49126</v>
       </c>
-      <c r="D14" s="5">
+      <c r="E14" s="1">
         <v>0.27189074235779964</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>2016</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="3">
         <v>7954162.8933319999</v>
       </c>
-      <c r="D15" s="5">
+      <c r="E15" s="1">
         <v>1.0345817282717262</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="10">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>2016</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="5">
         <v>70025142.648223996</v>
       </c>
-      <c r="D16" s="5">
+      <c r="E16" s="1">
         <v>9.108027340527066</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="10">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>2016</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="3">
         <v>933741.70418300002</v>
       </c>
-      <c r="D17" s="5">
+      <c r="E17" s="1">
         <v>0.1214498771307365</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>2018</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="3">
         <v>15966348.401390521</v>
       </c>
-      <c r="D18" s="5">
+      <c r="E18" s="1">
         <v>2.0727451448919707</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>2018</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="3">
         <v>3846201.282331232</v>
       </c>
-      <c r="D19" s="5">
+      <c r="E19" s="1">
         <v>0.50026754836652376</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="10">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>2018</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="3">
         <v>38096535.075953998</v>
       </c>
-      <c r="D20" s="5">
+      <c r="E20" s="1">
         <v>4.9551385392277787</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="10">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>2018</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="3">
         <v>1865843.0421264535</v>
       </c>
-      <c r="D21" s="5">
+      <c r="E21" s="1">
         <v>0.24268639517367618</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="10">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>2018</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="3">
         <v>2274848.1401110003</v>
       </c>
-      <c r="D22" s="5">
+      <c r="E22" s="1">
         <v>0.29588485324140407</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>2018</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="3">
         <v>7899474.1429020679</v>
       </c>
-      <c r="D23" s="5">
+      <c r="E23" s="1">
         <v>1.0274684741561673</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="10">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>2018</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="3">
         <v>81767580.166363999</v>
       </c>
-      <c r="D24" s="5">
+      <c r="E24" s="1">
         <v>10.635342215084663</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="10">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>2018</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="3">
         <v>2443.3930368423462</v>
       </c>
-      <c r="D25" s="5">
+      <c r="E25" s="1">
         <v>3.1780714385703542E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="10">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>2018</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="3">
         <v>68227.246643494931</v>
       </c>
-      <c r="D26" s="5">
+      <c r="E26" s="1">
         <v>8.8741786777866132E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="10">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>2020</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="3">
         <v>15981367.634475</v>
       </c>
-      <c r="D27" s="5">
+      <c r="E27" s="1">
         <v>2.0786639999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="10">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>2020</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="3">
         <v>3847644.780644</v>
       </c>
-      <c r="D28" s="5">
+      <c r="E28" s="1">
         <v>0.50045499999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="10">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29">
         <v>2020</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="3">
         <v>38190170.177658997</v>
       </c>
-      <c r="D29" s="5">
+      <c r="E29" s="1">
         <v>4.9673170000000004</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="10">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>2020</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="3">
         <v>1867856.6280509999</v>
       </c>
-      <c r="D30" s="5">
+      <c r="E30" s="1">
         <v>0.242948</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="10">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31">
         <v>2020</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="3">
         <v>2401391.8031859999</v>
       </c>
-      <c r="D31" s="5">
+      <c r="E31" s="1">
         <v>0.31234400000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="10">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32">
         <v>2020</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="3">
         <v>7924747.6106040003</v>
       </c>
-      <c r="D32" s="5">
+      <c r="E32" s="1">
         <v>1.030756</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="10">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33">
         <v>2020</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="3">
         <v>81450986.106517002</v>
       </c>
-      <c r="D33" s="5">
+      <c r="E33" s="1">
         <v>10.594163</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="10">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34">
         <v>2020</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="3">
         <v>2443.9246870000002</v>
       </c>
-      <c r="D34" s="5">
+      <c r="E34" s="1">
         <v>3.1799999999999998E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="10">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35">
         <v>2020</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="3">
         <v>214860.19404999999</v>
       </c>
-      <c r="D35" s="5">
+      <c r="E35" s="1">
         <v>2.7945999999999999E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="10">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36">
         <v>2020</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="4">
         <v>0.37529499999999999</v>
       </c>
-      <c r="D36" s="5">
+      <c r="E36" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="10">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37">
         <v>2022</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="3">
         <v>15830919.70597606</v>
       </c>
-      <c r="D37" s="5">
+      <c r="E37" s="1">
         <v>2.0590954047389709</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="10">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38">
         <v>2022</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="3">
         <v>3855902.8794670268</v>
       </c>
-      <c r="D38" s="5">
+      <c r="E38" s="1">
         <v>0.50152941507454873</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="10">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39">
         <v>2022</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="3">
         <v>39491130.284773447</v>
       </c>
-      <c r="D39" s="5">
+      <c r="E39" s="1">
         <v>5.1365306885252409</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="10">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40">
         <v>2022</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="3">
         <v>1874784.5107839089</v>
       </c>
-      <c r="D40" s="5">
+      <c r="E40" s="1">
         <v>0.24384939363779901</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="10">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41">
         <v>2022</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="3">
         <v>2477433.212338862</v>
       </c>
-      <c r="D41" s="5">
+      <c r="E41" s="1">
         <v>0.3222346798429509</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="10">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42">
         <v>2022</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="3">
         <v>8002906.0746674333</v>
       </c>
-      <c r="D42" s="5">
+      <c r="E42" s="1">
         <v>1.040921653887531</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="10">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43">
         <v>2022</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="3">
         <v>98133221.821008936</v>
       </c>
-      <c r="D43" s="5">
+      <c r="E43" s="1">
         <v>12.763987807201829</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="10">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44">
         <v>2022</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="3">
         <v>2824.9705899104779</v>
       </c>
-      <c r="D44" s="5">
+      <c r="E44" s="1">
         <v>3.6743815698917181E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="10">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45">
         <v>2022</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" t="s">
         <v>12</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="3">
         <v>272138.44219099899</v>
       </c>
-      <c r="D45" s="5">
+      <c r="E45" s="1">
         <v>3.5396491560548998E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="10">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46">
         <v>2022</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="3">
         <v>0.37529582351708701</v>
       </c>
-      <c r="D46" s="5">
+      <c r="E46" s="1">
         <v>4.8813961999999997E-8</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="10">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47">
         <v>2024</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" t="s">
         <v>3</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="2">
         <v>16015028.347584361</v>
       </c>
-      <c r="D47" s="1">
+      <c r="E47" s="1">
         <v>2.08833</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="10">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48">
         <v>2024</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" t="s">
         <v>4</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" s="2">
         <v>3867150.8787690001</v>
       </c>
-      <c r="D48" s="1">
+      <c r="E48" s="1">
         <v>0.50299199999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="10">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49">
         <v>2024</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" t="s">
         <v>10</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" s="2">
         <v>39564238.528729998</v>
       </c>
-      <c r="D49" s="1">
+      <c r="E49" s="1">
         <v>5.1460400000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="10">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50">
         <v>2024</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="2">
         <v>2454996.3419929999</v>
       </c>
-      <c r="D50" s="1">
+      <c r="E50" s="1">
         <v>0.31931599999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="10">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51">
         <v>2024</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="2">
         <v>4394467.1264840001</v>
       </c>
-      <c r="D51" s="1">
+      <c r="E51" s="1">
         <v>0.57157899999999995</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="10">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52">
         <v>2024</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" s="2">
         <v>7248957.8468709998</v>
       </c>
-      <c r="D52" s="1">
+      <c r="E52" s="1">
         <v>0.94285699999999995</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="10">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53">
         <v>2024</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="2">
         <v>99937978.161133006</v>
       </c>
-      <c r="D53" s="1">
+      <c r="E53" s="1">
         <v>12.998729000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="10">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54">
         <v>2024</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2">
         <v>2824.9706209999999</v>
       </c>
-      <c r="D54" s="1">
+      <c r="E54" s="1">
         <v>3.6699999999999998E-4</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="10">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55">
         <v>2024</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" s="2">
         <v>6760.2424060000003</v>
       </c>
-      <c r="D55" s="1">
+      <c r="E55" s="1">
         <v>8.7900000000000001E-4</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="10">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56">
         <v>2024</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" t="s">
         <v>13</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="6">
         <v>1065.4068070000001</v>
       </c>
-      <c r="D56" s="1">
+      <c r="E56" s="1">
         <v>1.3899999999999999E-4</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="10"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
